--- a/BWI/bestwine_output/bestwine_Gibraltar.xlsx
+++ b/BWI/bestwine_output/bestwine_Gibraltar.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2167,224 @@
       <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lewis Stagnetto Limited</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Lewis Stagnetto Limited</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7379</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41 Main Street</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>GX11 1AA</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stagnetto.com</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>mail@stagnetto.com</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>+350 200 78666</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>00166</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/stagnetto.events</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewis.stagnetto</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/LewisStagnetto</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Peter Stagnetto</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-stagnetto-069964144/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Lewis Stagnetto Limited</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Lewis Stagnetto Limited</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7379</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41 Main Street</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>GX11 1AA</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stagnetto.com</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>mail@stagnetto.com</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>+350 200 78666</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>00166</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/stagnetto.events</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewis.stagnetto</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/LewisStagnetto</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Maurice Stagnetto</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maurice-stagnetto-2aa18ab/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
